--- a/data/trans_dic/P36$huevo-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36$huevo-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón</t>
+          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,28</t>
+          <t>1,32; 3,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,31</t>
+          <t>2,92; 5,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,03</t>
+          <t>2,39; 5,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,02</t>
+          <t>0,71; 1,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,82</t>
+          <t>1,23; 2,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,69</t>
+          <t>2,94; 5,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,23</t>
+          <t>1,14; 2,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,54</t>
+          <t>2,17; 3,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,01</t>
+          <t>3,1; 4,98</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,77</t>
+          <t>3,62; 5,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,77</t>
+          <t>3,82; 5,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,56</t>
+          <t>7,14; 9,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,96</t>
+          <t>2,21; 3,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,72</t>
+          <t>2,03; 3,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,08</t>
+          <t>5,69; 8,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 4,61</t>
+          <t>3,12; 4,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,53</t>
+          <t>3,23; 4,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,78; 8,5</t>
+          <t>6,76; 8,47</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,39</t>
+          <t>1,94; 5,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,46</t>
+          <t>1,27; 4,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 11,71</t>
+          <t>6,69; 11,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,58</t>
+          <t>0,75; 3,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,2</t>
+          <t>0,51; 3,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 8,46</t>
+          <t>4,2; 8,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,79</t>
+          <t>1,64; 3,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,16</t>
+          <t>1,29; 3,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 9,15</t>
+          <t>5,95; 9,48</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,34</t>
+          <t>2,95; 4,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,9</t>
+          <t>3,6; 5,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,54; 8,37</t>
+          <t>6,45; 8,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,64</t>
+          <t>1,65; 2,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,88</t>
+          <t>1,8; 2,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 6,86</t>
+          <t>5,19; 6,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,28</t>
+          <t>2,43; 3,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,71</t>
+          <t>2,84; 3,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,29</t>
+          <t>6,06; 7,24</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón</t>
+          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14094; 33736</t>
+          <t>13584; 33651</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27569; 51602</t>
+          <t>28406; 53026</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18547; 37855</t>
+          <t>17992; 38622</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9073; 26587</t>
+          <t>9354; 25058</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17019; 37662</t>
+          <t>16444; 37288</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30001; 56480</t>
+          <t>29183; 55797</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27235; 52250</t>
+          <t>26587; 51993</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49515; 81833</t>
+          <t>50186; 82481</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54238; 87473</t>
+          <t>54129; 86870</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61451; 97576</t>
+          <t>61341; 97172</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75518; 113114</t>
+          <t>74826; 112012</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>148713; 198247</t>
+          <t>148018; 198268</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34606; 62792</t>
+          <t>35112; 62535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36207; 65353</t>
+          <t>35586; 66396</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>115453; 160555</t>
+          <t>112940; 160244</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>104696; 151014</t>
+          <t>102310; 148443</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>120946; 168304</t>
+          <t>120018; 164970</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>275421; 345051</t>
+          <t>274563; 344045</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10533; 29617</t>
+          <t>10652; 27958</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7009; 21432</t>
+          <t>6100; 21395</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35678; 64060</t>
+          <t>36572; 62013</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3317; 17033</t>
+          <t>3560; 16974</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2808; 14618</t>
+          <t>2330; 15660</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22223; 46479</t>
+          <t>23044; 45853</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17628; 38840</t>
+          <t>16812; 38790</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10967; 29646</t>
+          <t>12096; 30699</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63836; 100278</t>
+          <t>65267; 103895</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>99597; 142048</t>
+          <t>96616; 143034</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>120220; 167324</t>
+          <t>122919; 171044</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>220483; 282535</t>
+          <t>217610; 279609</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55194; 89177</t>
+          <t>55733; 89664</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63711; 102171</t>
+          <t>63798; 102506</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>181178; 242005</t>
+          <t>183019; 240734</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>162591; 218052</t>
+          <t>161452; 216795</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>197586; 258156</t>
+          <t>197555; 260064</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>419140; 503117</t>
+          <t>418108; 500077</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$huevo-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36$huevo-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,27</t>
+          <t>1,35; 3,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,45</t>
+          <t>2,88; 5,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,13</t>
+          <t>2,46; 5,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,91</t>
+          <t>0,69; 1,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,79</t>
+          <t>1,21; 2,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,62</t>
+          <t>2,84; 5,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,22</t>
+          <t>1,17; 2,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,57</t>
+          <t>2,12; 3,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 4,98</t>
+          <t>3,11; 4,9</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 5,74</t>
+          <t>3,61; 5,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,71</t>
+          <t>3,84; 5,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 9,56</t>
+          <t>7,23; 9,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,94</t>
+          <t>2,17; 3,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,78</t>
+          <t>2,13; 3,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,07</t>
+          <t>5,81; 8,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,53</t>
+          <t>3,16; 4,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 4,44</t>
+          <t>3,27; 4,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,47</t>
+          <t>6,81; 8,53</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,09</t>
+          <t>1,88; 5,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,46</t>
+          <t>1,39; 4,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 11,34</t>
+          <t>6,39; 11,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,56</t>
+          <t>0,7; 3,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,42</t>
+          <t>0,61; 3,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,35</t>
+          <t>3,99; 8,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,78</t>
+          <t>1,64; 3,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,27</t>
+          <t>1,21; 3,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 9,48</t>
+          <t>5,97; 9,32</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,37</t>
+          <t>2,94; 4,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,01</t>
+          <t>3,58; 4,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 8,29</t>
+          <t>6,45; 8,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,66</t>
+          <t>1,64; 2,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,89</t>
+          <t>1,84; 2,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 6,82</t>
+          <t>5,17; 6,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,26</t>
+          <t>2,44; 3,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,74</t>
+          <t>2,81; 3,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,06; 7,24</t>
+          <t>6,03; 7,24</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13584; 33651</t>
+          <t>13902; 33576</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28406; 53026</t>
+          <t>28041; 52353</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17992; 38622</t>
+          <t>18545; 39598</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9354; 25058</t>
+          <t>9026; 24803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16444; 37288</t>
+          <t>16169; 37569</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29183; 55797</t>
+          <t>28200; 55139</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26587; 51993</t>
+          <t>27388; 54849</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50186; 82481</t>
+          <t>48976; 80614</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54129; 86870</t>
+          <t>54292; 85578</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61341; 97172</t>
+          <t>61046; 97112</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74826; 112012</t>
+          <t>75263; 112070</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>148018; 198268</t>
+          <t>150031; 201010</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35112; 62535</t>
+          <t>34341; 62829</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35586; 66396</t>
+          <t>37294; 67426</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>112940; 160244</t>
+          <t>115421; 162588</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>102310; 148443</t>
+          <t>103543; 149600</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>120018; 164970</t>
+          <t>121426; 168292</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>274563; 344045</t>
+          <t>276384; 346482</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10652; 27958</t>
+          <t>10347; 28754</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6100; 21395</t>
+          <t>6696; 20944</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36572; 62013</t>
+          <t>34930; 62143</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3560; 16974</t>
+          <t>3319; 15876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2330; 15660</t>
+          <t>2804; 15504</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23044; 45853</t>
+          <t>21930; 46170</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16812; 38790</t>
+          <t>16825; 39086</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12096; 30699</t>
+          <t>11336; 29542</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65267; 103895</t>
+          <t>65476; 102189</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>96616; 143034</t>
+          <t>96059; 140992</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>122919; 171044</t>
+          <t>122375; 170026</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>217610; 279609</t>
+          <t>217447; 280190</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55733; 89664</t>
+          <t>55299; 88606</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63798; 102506</t>
+          <t>65160; 102486</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>183019; 240734</t>
+          <t>182461; 241569</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>161452; 216795</t>
+          <t>162356; 215852</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>197555; 260064</t>
+          <t>195871; 257529</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>418108; 500077</t>
+          <t>415938; 500066</t>
         </is>
       </c>
     </row>
